--- a/InputData/elec/BSfGBP/BAU Subsidy for Grid Battery Production.xlsx
+++ b/InputData/elec/BSfGBP/BAU Subsidy for Grid Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BSfGBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE830CDA-2171-4933-BA48-7F50760EB19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE71D76-7912-4BEC-A1F3-57F92E3FE77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Sources:</t>
   </si>
@@ -74,18 +74,6 @@
   </si>
   <si>
     <t>In the US, the Inflation Reduction Act includes a credit of $35/kWh for battery cells and $10/kWh for assembly for grid</t>
-  </si>
-  <si>
-    <t>Policy Setting (2023 USD)</t>
-  </si>
-  <si>
-    <t>FoPITY</t>
-  </si>
-  <si>
-    <t>("Schedule 3",(2021,0),(2024,0),</t>
-  </si>
-  <si>
-    <t>(2033,0),(2050,0)),</t>
   </si>
 </sst>
 </file>
@@ -460,17 +448,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,37 +466,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>0.75350342301658668</v>
       </c>
@@ -516,7 +504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>0.73</v>
       </c>
@@ -524,7 +512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>0.03</v>
       </c>
@@ -540,9 +528,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33CFD9F-5CAA-490F-A0C6-0C0A5236B09C}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>2023</v>
       </c>
@@ -574,7 +562,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -616,13 +604,13 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -717,7 +705,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -768,178 +756,76 @@
         <v>6436.4923393820782</v>
       </c>
       <c r="N2">
+        <f>$E2*(1-About!$A$14)^(N1-$E1)*'Phase Out'!L3</f>
         <v>0</v>
       </c>
       <c r="O2">
+        <f>$E2*(1-About!$A$14)^(O1-$E1)*'Phase Out'!M3</f>
         <v>0</v>
       </c>
       <c r="P2">
+        <f>$E2*(1-About!$A$14)^(P1-$E1)*'Phase Out'!N3</f>
         <v>0</v>
       </c>
       <c r="Q2">
+        <f>$E2*(1-About!$A$14)^(Q1-$E1)*'Phase Out'!O3</f>
         <v>0</v>
       </c>
       <c r="R2">
+        <f>$E2*(1-About!$A$14)^(R1-$E1)*'Phase Out'!P3</f>
         <v>0</v>
       </c>
       <c r="S2">
+        <f>$E2*(1-About!$A$14)^(S1-$E1)*'Phase Out'!Q3</f>
         <v>0</v>
       </c>
       <c r="T2">
+        <f>$E2*(1-About!$A$14)^(T1-$E1)*'Phase Out'!R3</f>
         <v>0</v>
       </c>
       <c r="U2">
+        <f>$E2*(1-About!$A$14)^(U1-$E1)*'Phase Out'!S3</f>
         <v>0</v>
       </c>
       <c r="V2">
+        <f>$E2*(1-About!$A$14)^(V1-$E1)*'Phase Out'!T3</f>
         <v>0</v>
       </c>
       <c r="W2">
+        <f>$E2*(1-About!$A$14)^(W1-$E1)*'Phase Out'!U3</f>
         <v>0</v>
       </c>
       <c r="X2">
+        <f>$E2*(1-About!$A$14)^(X1-$E1)*'Phase Out'!V3</f>
         <v>0</v>
       </c>
       <c r="Y2">
+        <f>$E2*(1-About!$A$14)^(Y1-$E1)*'Phase Out'!W3</f>
         <v>0</v>
       </c>
       <c r="Z2">
+        <f>$E2*(1-About!$A$14)^(Z1-$E1)*'Phase Out'!X3</f>
         <v>0</v>
       </c>
       <c r="AA2">
+        <f>$E2*(1-About!$A$14)^(AA1-$E1)*'Phase Out'!Y3</f>
         <v>0</v>
       </c>
       <c r="AB2">
+        <f>$E2*(1-About!$A$14)^(AB1-$E1)*'Phase Out'!Z3</f>
         <v>0</v>
       </c>
       <c r="AC2">
+        <f>$E2*(1-About!$A$14)^(AC1-$E1)*'Phase Out'!AA3</f>
         <v>0</v>
       </c>
       <c r="AD2">
+        <f>$E2*(1-About!$A$14)^(AD1-$E1)*'Phase Out'!AB3</f>
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4">
-        <f>F2/About!$A$12/1000</f>
-        <v>42.28846084392449</v>
-      </c>
-      <c r="G4">
-        <f>G2/About!$A$12/1000</f>
-        <v>41.019807018606755</v>
-      </c>
-      <c r="H4">
-        <f>H2/About!$A$12/1000</f>
-        <v>39.789212808048553</v>
-      </c>
-      <c r="I4">
-        <f>I2/About!$A$12/1000</f>
-        <v>38.595536423807097</v>
-      </c>
-      <c r="J4">
-        <f>J2/About!$A$12/1000</f>
-        <v>37.437670331092889</v>
-      </c>
-      <c r="K4">
-        <f>K2/About!$A$12/1000</f>
-        <v>27.235905165870069</v>
-      </c>
-      <c r="L4">
-        <f>L2/About!$A$12/1000</f>
-        <v>17.612552007262646</v>
-      </c>
-      <c r="M4">
-        <f>M2/About!$A$12/1000</f>
-        <v>8.5420877235223838</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <f t="shared" ref="E5:M5" si="0">F4/MAX($D$4:$M$4)</f>
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>0.97</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>0.94090000000000007</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>0.91267300000000007</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="0"/>
-        <v>0.88529281000000015</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>0.6440505192749999</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="0"/>
-        <v>0.41648600246450002</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>0.20199571119528251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="str">
-        <f t="shared" ref="E6:M6" si="1">CONCATENATE("(",F1,",",F5,"),")</f>
-        <v>(2025,1),</v>
-      </c>
-      <c r="G6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2026,0.97),</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2027,0.9409),</v>
-      </c>
-      <c r="I6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2028,0.912673),</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2029,0.88529281),</v>
-      </c>
-      <c r="K6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2030,0.644050519275),</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2031,0.4164860024645),</v>
-      </c>
-      <c r="M6" t="str">
-        <f t="shared" si="1"/>
-        <v>(2032,0.201995711195283),</v>
-      </c>
-      <c r="N6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C7" t="str">
-        <f>CONCATENATE(C6,F6,G6,H6,I6,J6,K6,L6,M6,N6)</f>
-        <v>("Schedule 3",(2021,0),(2024,0),(2025,1),(2026,0.97),(2027,0.9409),(2028,0.912673),(2029,0.88529281),(2030,0.644050519275),(2031,0.4164860024645),(2032,0.201995711195283),(2033,0),(2050,0)),</v>
+        <f>$E2*(1-About!$A$14)^(AE1-$E1)*'Phase Out'!AC3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
